--- a/sample-data/08-workbook.xlsx
+++ b/sample-data/08-workbook.xlsx
@@ -245,7 +245,7 @@
         </is>
       </c>
       <c r="F2" s="1">
-        <v>34249</v>
+        <v>34256</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -296,10 +296,10 @@
         </is>
       </c>
       <c r="S2" s="1">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="T2" s="1">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="U2">
         <v>1000000</v>
@@ -359,7 +359,7 @@
         </is>
       </c>
       <c r="F3" s="1">
-        <v>34249</v>
+        <v>34256</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -410,10 +410,10 @@
         </is>
       </c>
       <c r="S3" s="1">
-        <v>45904</v>
+        <v>45911</v>
       </c>
       <c r="T3" s="1">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="U3">
         <v>1500000</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="F4" s="1">
-        <v>34249</v>
+        <v>34256</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="S4" s="1">
-        <v>45922</v>
+        <v>45929</v>
       </c>
       <c r="T4" s="1">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="U4">
         <v>720000</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F5" s="1">
-        <v>34249</v>
+        <v>34256</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="S5" s="1">
-        <v>45943</v>
+        <v>45950</v>
       </c>
       <c r="T5" s="1">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="U5">
         <v>2500000</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F6" s="1">
-        <v>34249</v>
+        <v>34256</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="S6" s="1">
-        <v>45873</v>
+        <v>45880</v>
       </c>
       <c r="T6" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="U6">
         <v>480000</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="F7" s="1">
-        <v>34249</v>
+        <v>34256</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="S7" s="1">
-        <v>45967</v>
+        <v>45974</v>
       </c>
       <c r="T7" s="1">
-        <v>46331</v>
+        <v>46338</v>
       </c>
       <c r="U7">
         <v>2000000</v>
@@ -970,12 +970,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/08/2025</t>
+          <t xml:space="preserve">02/09/2025</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t xml:space="preserve">26/08/2026</t>
+          <t xml:space="preserve">02/09/2026</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
